--- a/04_regulatory-compliance-for-ai-eu-ai-act/exercises/starter/compliance_plan.xlsx
+++ b/04_regulatory-compliance-for-ai-eu-ai-act/exercises/starter/compliance_plan.xlsx
@@ -581,7 +581,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -667,8 +666,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -993,37 +990,37 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hint: What documentation exists for TalentScope AI's architecture, algorithms, and data flows?</t>
+          <t>[Your response here — name the technical document that covers TalentScope AI's architecture, algorithms, and data flows.]</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Hint: Implemented/Partial/Gap?</t>
+          <t>[Your response here — choose Implemented / Partial / Gap based on how complete that documentation currently is.]</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Hint: Evidence file reference</t>
+          <t>[Your response here — cite the evidence file (e.g., TR-00X-*.pdf) where this documentation lives.]</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Hint: Is the documentation complete? Up to date? Does it cover the video analysis component?</t>
+          <t>[Your response here — describe what is missing or outdated — pay attention to whether the video-analysis component is covered.]</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>Hint: What needs to be created or updated?</t>
+          <t>[Your response here — describe what documentation needs to be created or refreshed and to what depth (Article 11 + Annex IV).]</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>Hint: Responsible team</t>
+          <t>[Your response here — name the function accountable (e.g., ML Engineering, Product, Documentation).]</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>Hint: Target date</t>
+          <t>[Your response here — pick a realistic target date (YYYY-MM-DD) based on the urgency of the gap.]</t>
         </is>
       </c>
     </row>
@@ -1050,37 +1047,37 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Hint: The audit found NO formal risk management system. What needs to be built?</t>
+          <t>[Your response here — describe the risk management system that needs to be built — the audit found none exists.]</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Hint: Given there's nothing in place, what status?</t>
+          <t>[Your response here — choose Implemented / Partial / Gap given that nothing is in place today.]</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Hint: Evidence reference</t>
+          <t>[Your response here — cite the evidence file (or note 'planned' if it doesn't exist yet).]</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Hint: Major gap — no risk management framework exists for AI components</t>
+          <t>[Your response here — describe the gap — no risk management framework exists for the AI components.]</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>Hint: What framework to implement? Consider NIST AI RMF or ISO 31000</t>
+          <t>[Your response here — name the framework you'd adopt (consider NIST AI RMF or ISO 31000) and the rollout steps.]</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>Hint: Team</t>
+          <t>[Your response here — name the function accountable (e.g., Risk, Compliance, ML Engineering).]</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — pick a realistic target date (YYYY-MM-DD) — major framework build, plan accordingly.]</t>
         </is>
       </c>
     </row>
@@ -1107,37 +1104,37 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Hint: How do you ensure the screening is accurate? The audit found 8% gender disparity — what controls address this?</t>
+          <t>[Your response here — describe the controls that ensure screening accuracy — and what addresses the 8% gender disparity finding from the audit.]</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status given the bias finding?</t>
+          <t>[Your response here — choose Implemented / Partial / Gap given the bias finding from the third-party audit.]</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Hint: Evidence reference</t>
+          <t>[Your response here — cite the evidence file that documents accuracy / bias testing (or planned test reports).]</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Hint: 8% gender disparity in video analysis. What other biases haven't been tested?</t>
+          <t>[Your response here — describe the gap — 8% gender disparity confirmed, plus any untested protected attributes.]</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>Hint: Bias remediation plan — testing, thresholds, monitoring</t>
+          <t>[Your response here — outline the bias remediation plan — testing scope, thresholds, and ongoing monitoring.]</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>Hint: Team</t>
+          <t>[Your response here — name the function accountable (e.g., ML Engineering, Data Science, Ethics).]</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — pick a realistic target date (YYYY-MM-DD) — bias remediation is time-sensitive.]</t>
         </is>
       </c>
     </row>
@@ -1164,37 +1161,37 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Hint: What logging exists for screening decisions, candidate interactions, and model predictions?</t>
+          <t>[Your response here — describe the logging in place for screening decisions, candidate interactions, and model predictions.]</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status?</t>
+          <t>[Your response here — choose Implemented / Partial / Gap based on coverage of the logs you described.]</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>Hint: Evidence reference</t>
+          <t>[Your response here — cite the evidence file or logging-system reference.]</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Hint: Are logs sufficient for regulatory audit? Do they cover video analysis decisions?</t>
+          <t>[Your response here — describe whether logs are sufficient for regulatory audit and whether video-analysis decisions are captured.]</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>Hint: What additional logging is needed?</t>
+          <t>[Your response here — describe what additional logging is needed (events, fields, retention).]</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>Hint: Team</t>
+          <t>[Your response here — name the function accountable (e.g., Platform Engineering, SRE, ML Engineering).]</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — pick a realistic target date (YYYY-MM-DD).]</t>
         </is>
       </c>
     </row>
@@ -1221,37 +1218,37 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Hint: Has a conformity assessment been done? What evidence exists?</t>
+          <t>[Your response here — describe whether a conformity assessment has been conducted and what evidence supports it.]</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Hint: The scenario says no assessment has been conducted...</t>
+          <t>[Your response here — choose Implemented / Partial / Gap — the scenario states no assessment has been done.]</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Hint: Evidence reference</t>
+          <t>[Your response here — cite the evidence file (or note 'planned' if no assessment exists).]</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Hint: This is a major gap — no conformity assessment exists at all</t>
+          <t>[Your response here — describe the gap — no conformity assessment has been completed.]</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>Hint: Full conformity assessment process needed. Internal or third-party?</t>
+          <t>[Your response here — outline the conformity assessment plan and decide internal vs third-party route.]</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>Hint: Team</t>
+          <t>[Your response here — name the function accountable (e.g., Compliance, Legal, Quality).]</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — pick a realistic target date (YYYY-MM-DD) — this blocks high-risk deployment.]</t>
         </is>
       </c>
     </row>
@@ -1278,37 +1275,37 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Has TalentScope AI been registered in the EU database for high-risk AI systems?</t>
+          <t>[Your response here — describe whether TalentScope AI has been registered in the EU AI database for high-risk systems.]</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status?</t>
+          <t>[Your response here — choose Implemented / Partial / Gap based on registration status.]</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Evidence reference</t>
+          <t>[Your response here — cite the evidence file (registration certificate or 'planned').]</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Consider whether registration can happen before conformity assessment is complete</t>
+          <t>[Your response here — describe the dependency — registration typically follows the conformity assessment.]</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Registration steps and timeline</t>
+          <t>[Your response here — outline the registration steps and the realistic timeline relative to the conformity assessment.]</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Team</t>
+          <t>[Your response here — name the function accountable (e.g., Legal, Compliance).]</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — pick a realistic target date (YYYY-MM-DD) — typically after conformity assessment.]</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1317,12 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Bias Prevention — Identify and mitigate discriminatory outcomes</t>
+          <t>Bias-relevant data quality — examine training datasets for biases and apply detection / mitigation measures</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Article 15(2)</t>
+          <t>Article 10(2)(f)–(g)</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -1335,37 +1332,37 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Hint: What frameworks exist for testing bias? The video analysis has known gender disparity...</t>
+          <t>[Your response here — describe the framework used to test for bias across protected attributes in training data.]</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Given the 8% disparity finding?</t>
+          <t>[Your response here — choose Implemented / Partial / Gap given the 8% disparity finding.]</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Evidence reference</t>
+          <t>[Your response here — cite the evidence file (bias audit, fairness test results, or planned report).]</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Gender disparity confirmed. What about race, age, disability, accent in video analysis?</t>
+          <t>[Your response here — describe the gap — gender confirmed; what about race, age, disability, accent in video analysis?]</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Comprehensive fairness testing plan across all protected characteristics</t>
+          <t>[Your response here — outline a comprehensive fairness testing plan covering all protected characteristics.]</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Team</t>
+          <t>[Your response here — name the function accountable (e.g., Data Science, Ethics, ML Engineering).]</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — pick a realistic target date (YYYY-MM-DD).]</t>
         </is>
       </c>
     </row>
@@ -1392,37 +1389,37 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Hint: Candidates subject to automated screening have rights under GDPR Art 22. What mechanisms exist?</t>
+          <t>[Your response here — describe the mechanisms that give candidates their GDPR Art 22 rights (human review, contest decisions).]</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Hint: Are candidates informed of their right to human review? Can they contest decisions?</t>
+          <t>[Your response here — choose Implemented / Partial / Gap — are candidates informed of their right to human review?]</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Hint: Evidence reference</t>
+          <t>[Your response here — cite the evidence file (notice text, appeal SOP, or planned doc).]</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Hint: The scenario says candidates aren't even informed AI is used — this extends to GDPR rights too</t>
+          <t>[Your response here — describe the gap — candidates aren't even informed AI is used, so GDPR rights are also unmet.]</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Hint: Candidate rights notification + appeal mechanism</t>
+          <t>[Your response here — outline the candidate-rights notification plus appeal/contest mechanism.]</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>Hint: Team</t>
+          <t>[Your response here — name the function accountable (e.g., Legal, Privacy, Product).]</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — pick a realistic target date (YYYY-MM-DD).]</t>
         </is>
       </c>
     </row>
@@ -1449,37 +1446,37 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Hint: What monitoring exists for TalentScope AI in production? Performance dashboards? Drift detection?</t>
+          <t>[Your response here — describe the production monitoring for TalentScope AI — dashboards, drift detection, performance metrics.]</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status?</t>
+          <t>[Your response here — choose Implemented / Partial / Gap based on monitoring coverage.]</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Hint: Evidence reference</t>
+          <t>[Your response here — cite the evidence file (dashboard link, monitoring report, or planned).]</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Hint: Is there automated monitoring? Are performance metrics tracked over time?</t>
+          <t>[Your response here — describe whether automated monitoring exists and whether metrics are tracked over time.]</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>Hint: Monitoring and alerting infrastructure needed</t>
+          <t>[Your response here — outline the monitoring and alerting infrastructure needed for ongoing surveillance.]</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>Hint: Team</t>
+          <t>[Your response here — name the function accountable (e.g., ML Engineering, SRE, Compliance).]</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — pick a realistic target date (YYYY-MM-DD).]</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1503,22 @@
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>Hint: What incident-detection and reporting pipeline exists for TalentScope AI? Article 73 requires notification to the national competent authority within 15 days of becoming aware of a serious incident.</t>
+          <t>[Your response here — describe the incident-detection and 15-day reporting pipeline needed for Article 73 notifications to the national competent authority.]</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>Hint: Status given that Article 73 enforces in Aug 2026?</t>
+          <t>[Your response here — choose Implemented / Partial / Gap given Article 73 enforces in Aug 2026.]</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>Hint: Evidence reference</t>
+          <t>[Your response here — cite the evidence file (workflow doc, SOP, or 'planned').]</t>
         </is>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>Hint: Without an incident-detection-and-reporting workflow, the company will be non-compliant when Article 73 enforces. Plan a 15-day reporting SLA + designate a notifying authority lead.</t>
+          <t>[Your response here — describe the gap and plan the 15-day reporting SLA plus designated notifying-authority lead; consider integration with the M6 incident-response work.]</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1730,32 +1727,32 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Hint: System Architecture or Technical Spec?</t>
+          <t>[Your response here — name the evidence type (System Architecture, Technical Spec, etc.).]</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Hint: What's the main technical document for TalentScope AI?</t>
+          <t>[Your response here — name the main technical document for TalentScope AI.]</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hint: /path/</t>
+          <t>[Your response here — give the storage location (e.g., /compliance/technical/).]</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — give the last-updated date (YYYY-MM-DD).]</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Hint: Is it current?</t>
+          <t>[Your response here — set the status (Approved / In Progress / Planned / Outdated).]</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Hint: Does it cover the video analysis ML pipeline?</t>
+          <t>[Your response here — note whether the document covers the video-analysis ML pipeline.]</t>
         </is>
       </c>
     </row>
@@ -1772,32 +1769,32 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Hint: Risk Register? Framework Document?</t>
+          <t>[Your response here — name the evidence type (Risk Register, Framework Document, etc.) — remember none exists yet.]</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Hint: Remember — no formal risk management exists yet</t>
+          <t>[Your response here — name the document or placeholder — no formal risk management exists yet.]</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Hint: /path/</t>
+          <t>[Your response here — give the planned storage location (e.g., /compliance/risk/).]</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — give the date or target quarter.]</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Hint: Does this evidence exist yet?</t>
+          <t>[Your response here — set the status — does this evidence exist yet?]</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Hint: If no evidence exists, what's the status?</t>
+          <t>[Your response here — note the implication for status when no evidence exists.]</t>
         </is>
       </c>
     </row>
@@ -1814,32 +1811,32 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Hint: Test Results? Bias Audit?</t>
+          <t>[Your response here — name the evidence type (Test Results, Bias Audit, etc.).]</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Hint: The third-party audit report IS evidence — of the problem</t>
+          <t>[Your response here — name the document — the third-party audit report is itself evidence (of the problem).]</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Hint: /path/</t>
+          <t>[Your response here — give the storage location.]</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — give the date (YYYY-MM-DD).]</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status?</t>
+          <t>[Your response here — set the status (Approved / In Progress / Planned).]</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Hint: Document both the audit findings AND what remediation testing is planned</t>
+          <t>[Your response here — document both the audit findings AND the planned remediation testing.]</t>
         </is>
       </c>
     </row>
@@ -1856,32 +1853,32 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Hint: System Logs? Audit Trail?</t>
+          <t>[Your response here — name the evidence type (System Logs, Audit Trail, etc.).]</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Hint: What logging infrastructure exists?</t>
+          <t>[Your response here — name the logging infrastructure or log-management document.]</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Hint: /path/</t>
+          <t>[Your response here — give the storage location.]</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — give the date (YYYY-MM-DD).]</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status?</t>
+          <t>[Your response here — set the status.]</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Hint: Are logs granular enough for regulatory review?</t>
+          <t>[Your response here — note whether logs are granular enough for regulatory review.]</t>
         </is>
       </c>
     </row>
@@ -1898,32 +1895,32 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Hint: Assessment Report? Checklist?</t>
+          <t>[Your response here — name the evidence type (Assessment Report, Checklist, etc.).]</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Hint: No conformity assessment done — what evidence can you cite?</t>
+          <t>[Your response here — name the document — no conformity assessment is done, so cite the plan or placeholder.]</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Hint: /path/</t>
+          <t>[Your response here — give the storage location.]</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — give the date or planned date.]</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status?</t>
+          <t>[Your response here — set the status.]</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Hint: The gap itself is the finding. Document the plan to conduct the assessment.</t>
+          <t>[Your response here — document the gap itself plus the plan to conduct the assessment.]</t>
         </is>
       </c>
     </row>
@@ -1940,32 +1937,32 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Registration Certificate?</t>
+          <t>[Your response here — name the evidence type (Registration Certificate, etc.).]</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Has registration been submitted?</t>
+          <t>[Your response here — name the document — has registration been submitted?]</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Hint: /path/</t>
+          <t>[Your response here — give the storage location.]</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — give the date or planned date.]</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status?</t>
+          <t>[Your response here — set the status.]</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Hint: Registration typically follows conformity assessment</t>
+          <t>[Your response here — note the sequencing — registration typically follows conformity assessment.]</t>
         </is>
       </c>
     </row>
@@ -1982,32 +1979,32 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Bias Assessment Report?</t>
+          <t>[Your response here — name the evidence type (Bias Assessment Report, etc.).]</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Third-party audit + internal testing results</t>
+          <t>[Your response here — name the document — third-party audit plus any internal testing results.]</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Hint: /path/</t>
+          <t>[Your response here — give the storage location.]</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — give the date (YYYY-MM-DD).]</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status?</t>
+          <t>[Your response here — set the status.]</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Hint: Document the 8% gender disparity finding and remediation progress</t>
+          <t>[Your response here — document the 8% gender disparity finding and the remediation progress.]</t>
         </is>
       </c>
     </row>
@@ -2024,32 +2021,32 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Hint: Policy Document? Process Flow?</t>
+          <t>[Your response here — name the evidence type (Policy Document, Process Flow, etc.).]</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Hint: GDPR Art 22 rights documentation for candidates</t>
+          <t>[Your response here — name the GDPR Art 22 candidate-rights document.]</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Hint: /path/</t>
+          <t>[Your response here — give the storage location.]</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — give the date.]</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status?</t>
+          <t>[Your response here — set the status.]</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Hint: Does a candidate appeal/contest mechanism exist?</t>
+          <t>[Your response here — note whether a candidate appeal/contest mechanism currently exists.]</t>
         </is>
       </c>
     </row>
@@ -2066,32 +2063,74 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Hint: Dashboard? Monitoring Report?</t>
+          <t>[Your response here — name the evidence type (Dashboard, Monitoring Report, etc.).]</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Hint: Post-market monitoring evidence</t>
+          <t>[Your response here — name the post-market monitoring artifact.]</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Hint: /path/</t>
+          <t>[Your response here — give the storage location or system link.]</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Hint: Date</t>
+          <t>[Your response here — give the date.]</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Hint: Status?</t>
+          <t>[Your response here — set the status.]</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Hint: What production metrics are tracked? Are there alerting thresholds?</t>
+          <t>[Your response here — note which production metrics are tracked and whether alerting thresholds exist.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>EV-013</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>REQ-013</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>[Your response here — name the evidence type (Plan Document, Incident-Reporting Workflow, etc.).]</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>[Your response here — name the document that supports your Article 73 incident-reporting pipeline (draft is acceptable).]</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>[Your response here — give the storage location.]</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>[Your response here — give the date or target quarter.]</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>[Your response here — set the status given that Article 73 enforces in Aug 2026.]</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>[Your response here — document the 15-day reporting SLA, the notifying-authority lead, and any integration with the M6 incident-response work.]</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2161,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>

--- a/04_regulatory-compliance-for-ai-eu-ai-act/exercises/starter/compliance_plan.xlsx
+++ b/04_regulatory-compliance-for-ai-eu-ai-act/exercises/starter/compliance_plan.xlsx
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -200,6 +200,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1481,22 +1487,22 @@
       </c>
     </row>
     <row r="14" ht="100" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>REQ-013</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Serious-Incident Reporting — Notify national competent authority of serious incidents per Article 73 (enforces Aug 2026)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Article 73</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>High-Risk</t>
         </is>
@@ -1519,6 +1525,21 @@
       <c r="H14" s="16" t="inlineStr">
         <is>
           <t>[Your response here — describe the gap and plan the 15-day reporting SLA plus designated notifying-authority lead; consider integration with the M6 incident-response work.]</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — outline the remediation plan (15-day reporting SLA, escalation path, integration with incident detection).]</t>
+        </is>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — name the accountable function (e.g., DPO, Compliance, Incident Response).]</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — pick a realistic target date before Aug 2026 (YYYY-MM-DD).]</t>
         </is>
       </c>
     </row>
@@ -2283,17 +2304,17 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>General-Purpose AI models — including those with systemic risk. Added in 2026 EU AI Act refresh.</t>
+          <t>General-Purpose AI models — including those with systemic risk. Introduced by Regulation (EU) 2024/1689; obligations applicable from 2 Aug 2025.</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>Foundation-model APIs embedded in customer-facing assistants, chatbots, code copilots, RAG systems.</t>
+          <t>Providers of general-purpose foundation models — e.g. models offered via API that power customer-facing assistants, chatbots, code copilots, RAG systems.</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>Transparency to downstream deployers (Art. 53), copyright disclosure, technical documentation; if systemic risk, additional model evaluation + adversarial testing + Art. 55 obligations.</t>
+          <t>Provider obligations — transparency to downstream deployers (Art. 53), copyright disclosure, technical documentation; if systemic risk, additional model evaluation + adversarial testing + Art. 55 obligations.</t>
         </is>
       </c>
     </row>

--- a/04_regulatory-compliance-for-ai-eu-ai-act/exercises/starter/compliance_plan.xlsx
+++ b/04_regulatory-compliance-for-ai-eu-ai-act/exercises/starter/compliance_plan.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +76,14 @@
       <i val="1"/>
       <color rgb="007F6000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -155,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -206,6 +214,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2253,68 +2264,68 @@
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
+          <t>GPAI / Foundation Models
+(Articles 51–55)</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>General-Purpose AI models — including those with systemic risk. Introduced by Regulation (EU) 2024/1689; obligations applicable from 2 Aug 2025.</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Providers of general-purpose foundation models — e.g. models offered via API that power customer-facing assistants, chatbots, code copilots, RAG systems.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Provider obligations — transparency to downstream deployers (Art. 53), copyright disclosure, technical documentation; if systemic risk, additional model evaluation + adversarial testing + Art. 55 obligations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
           <t>Limited Risk
 (Article 50)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>AI systems with specific transparency obligations.</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Chatbots (must disclose AI), emotion recognition systems, deepfake generators, biometric categorization</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Must disclose to users they are interacting with AI. Limited documentation.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="75" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="8" ht="95" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Minimal Risk</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>AI systems with no specific regulatory requirements.</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Spam filters, AI video games, inventory management, basic recommendation engines, route optimization</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>No mandatory requirements. Voluntary codes of conduct encouraged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="95" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>GPAI / Foundation Models
-(Articles 51–55)</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>General-Purpose AI models — including those with systemic risk. Introduced by Regulation (EU) 2024/1689; obligations applicable from 2 Aug 2025.</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Providers of general-purpose foundation models — e.g. models offered via API that power customer-facing assistants, chatbots, code copilots, RAG systems.</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Provider obligations — transparency to downstream deployers (Art. 53), copyright disclosure, technical documentation; if systemic risk, additional model evaluation + adversarial testing + Art. 55 obligations.</t>
         </is>
       </c>
     </row>

--- a/04_regulatory-compliance-for-ai-eu-ai-act/exercises/starter/compliance_plan.xlsx
+++ b/04_regulatory-compliance-for-ai-eu-ai-act/exercises/starter/compliance_plan.xlsx
@@ -1505,7 +1505,7 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>Serious-Incident Reporting — Notify national competent authority of serious incidents per Article 73 (enforces Aug 2026)</t>
+          <t>Serious-Incident Reporting — Notify national competent authority of serious incidents per Article 73 (applies 2 Dec 2027)</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>[Your response here — choose Implemented / Partial / Gap given Article 73 enforces in Aug 2026.]</t>
+          <t>[Your response here — choose Implemented / Partial / Gap given Article 73 applies from 2 Dec 2027.]</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="K14" s="19" t="inlineStr">
         <is>
-          <t>[Your response here — pick a realistic target date before Aug 2026 (YYYY-MM-DD).]</t>
+          <t>[Your response here — pick a realistic target date before 2 Dec 2027 (YYYY-MM-DD).]</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>[Your response here — set the status given that Article 73 enforces in Aug 2026.]</t>
+          <t>[Your response here — set the status given that Article 73 applies from 2 Dec 2027.]</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
